--- a/Banco/Base_BANCO_TABAJARA.xlsx
+++ b/Banco/Base_BANCO_TABAJARA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Extrato</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Agencia</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Extrato</t>
         </is>
       </c>
     </row>
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44433322212</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>400</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -480,24 +480,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>juliete</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12359874199</t>
+          <t>43651334899</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>corrente</t>
+          <t>Corrente</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>322</v>
+      </c>
+      <c r="F3" t="n">
         <v>401</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -506,50 +506,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>josue</t>
+          <t>chuck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45612378955</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Corrente</t>
+          <t>corrente</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="n">
         <v>402</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Guilherme</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>43651334899</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Corrente</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>403</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
